--- a/ajout-exemple-decision-formation/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/ajout-exemple-decision-formation/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:38:17+00:00</t>
+    <t>2026-07-21T09:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
